--- a/trunk/plan/excel/魔法效果表.xlsx
+++ b/trunk/plan/excel/魔法效果表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25185" windowHeight="7995"/>
+    <workbookView windowWidth="27465" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="EffectCFG" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,40 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+// 魔法效果枚举,每种魔法效果对应一种效果的计算类型和表现形式</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -62,22 +94,43 @@
     <t>造成魔法伤害效果</t>
   </si>
   <si>
+    <t>持续魔法伤害效果</t>
+  </si>
+  <si>
     <t>治疗效果</t>
   </si>
   <si>
     <t>恢复生命值</t>
   </si>
   <si>
-    <t>狂暴增益</t>
+    <t>愈合效果</t>
+  </si>
+  <si>
+    <t>持续恢复生命值</t>
+  </si>
+  <si>
+    <t>狂暴增益启动</t>
   </si>
   <si>
     <t>提升攻击力</t>
   </si>
   <si>
-    <t>狂暴减益</t>
+    <t>狂暴增益结束</t>
+  </si>
+  <si>
+    <t>提升攻击力结束</t>
+  </si>
+  <si>
+    <t>狂暴减益启动</t>
   </si>
   <si>
     <t>减少护甲值</t>
+  </si>
+  <si>
+    <t>狂暴减益结束</t>
+  </si>
+  <si>
+    <t>减少护甲值结束</t>
   </si>
 </sst>
 </file>
@@ -90,7 +143,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +300,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1046,10 +1110,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="5" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="5" width="12.875" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1095,7 +1160,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
@@ -1112,48 +1177,126 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>50</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
+      </c>
+      <c r="F5" t="s">
         <v>13</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
+        <v>202</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>301</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E7">
         <v>15</v>
       </c>
-      <c r="C6">
+      <c r="F7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>302</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>15</v>
+      </c>
+      <c r="F8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>303</v>
+      </c>
+      <c r="B9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9">
         <v>5</v>
       </c>
-      <c r="F6" t="s">
-        <v>16</v>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>304</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/trunk/plan/excel/魔法效果表.xlsx
+++ b/trunk/plan/excel/魔法效果表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27465" windowHeight="8655"/>
+    <workbookView windowWidth="30585" windowHeight="8985"/>
   </bookViews>
   <sheets>
     <sheet name="EffectCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/魔法效果表.xlsx
+++ b/trunk/plan/excel/魔法效果表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30585" windowHeight="8985"/>
+    <workbookView windowWidth="22350" windowHeight="11055"/>
   </bookViews>
   <sheets>
     <sheet name="EffectCFG" sheetId="1" r:id="rId1"/>

--- a/trunk/plan/excel/魔法效果表.xlsx
+++ b/trunk/plan/excel/魔法效果表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22350" windowHeight="11055"/>
+    <workbookView windowWidth="27030" windowHeight="12825"/>
   </bookViews>
   <sheets>
     <sheet name="EffectCFG" sheetId="1" r:id="rId1"/>
@@ -54,12 +54,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+关联属性EnumAttrType</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -68,6 +90,9 @@
   </si>
   <si>
     <t>EffectType</t>
+  </si>
+  <si>
+    <t>TargetAttr</t>
   </si>
   <si>
     <t>BaseValue</t>
@@ -302,12 +327,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1110,15 +1135,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="5" width="12.875" customWidth="1"/>
-    <col min="6" max="6" width="17.125" customWidth="1"/>
+    <col min="3" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
+    <row r="1" ht="14.25" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1131,167 +1156,197 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>100</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
+      <c r="G3" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>50</v>
       </c>
-      <c r="F4" t="s">
-        <v>11</v>
+      <c r="G4" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>2</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>100</v>
       </c>
-      <c r="F5" t="s">
-        <v>13</v>
+      <c r="G5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>50</v>
       </c>
-      <c r="F6" t="s">
-        <v>15</v>
+      <c r="G6" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
-      <c r="E7">
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="F7">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
-        <v>17</v>
+      <c r="G7" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>302</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
-      <c r="E8">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>-15</v>
+      </c>
+      <c r="G8" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>303</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>5</v>
       </c>
-      <c r="F9" t="s">
-        <v>21</v>
+      <c r="G9" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>304</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
         <v>5</v>
       </c>
-      <c r="E10">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>23</v>
+      <c r="F10">
+        <v>-5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/trunk/plan/excel/魔法效果表.xlsx
+++ b/trunk/plan/excel/魔法效果表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27030" windowHeight="12825"/>
+    <workbookView windowWidth="24570" windowHeight="10290"/>
   </bookViews>
   <sheets>
     <sheet name="EffectCFG" sheetId="1" r:id="rId1"/>
@@ -327,12 +327,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/trunk/plan/excel/魔法效果表.xlsx
+++ b/trunk/plan/excel/魔法效果表.xlsx
@@ -76,12 +76,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特殊效果分类</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -101,6 +123,9 @@
     <t>ValueScale</t>
   </si>
   <si>
+    <t>SpecialType</t>
+  </si>
+  <si>
     <t>Desc</t>
   </si>
   <si>
@@ -156,6 +181,12 @@
   </si>
   <si>
     <t>减少护甲值结束</t>
+  </si>
+  <si>
+    <t>眩晕效果</t>
+  </si>
+  <si>
+    <t>造成眩晕效果</t>
   </si>
 </sst>
 </file>
@@ -338,7 +369,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,6 +378,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -532,12 +575,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -662,7 +720,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -674,121 +732,123 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1135,15 +1195,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="7" width="17.125" customWidth="1"/>
+    <col min="3" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:7">
+    <row r="1" ht="14.25" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1165,38 +1225,44 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3">
@@ -1205,18 +1271,21 @@
       <c r="E3">
         <v>100</v>
       </c>
-      <c r="G3" t="s">
-        <v>11</v>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4">
@@ -1225,18 +1294,21 @@
       <c r="E4">
         <v>50</v>
       </c>
-      <c r="G4" t="s">
-        <v>12</v>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2">
         <v>2</v>
       </c>
       <c r="D5">
@@ -1245,18 +1317,21 @@
       <c r="E5">
         <v>100</v>
       </c>
-      <c r="G5" t="s">
-        <v>14</v>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>202</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6">
@@ -1265,18 +1340,21 @@
       <c r="E6">
         <v>50</v>
       </c>
-      <c r="G6" t="s">
-        <v>16</v>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>301</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2">
         <v>4</v>
       </c>
       <c r="D7">
@@ -1285,18 +1363,21 @@
       <c r="F7">
         <v>15</v>
       </c>
-      <c r="G7" t="s">
-        <v>18</v>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>302</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8">
+        <v>20</v>
+      </c>
+      <c r="C8" s="2">
         <v>4</v>
       </c>
       <c r="D8">
@@ -1305,18 +1386,21 @@
       <c r="F8">
         <v>-15</v>
       </c>
-      <c r="G8" t="s">
-        <v>20</v>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>303</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9">
@@ -1325,18 +1409,21 @@
       <c r="F9">
         <v>5</v>
       </c>
-      <c r="G9" t="s">
-        <v>22</v>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>304</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2">
         <v>4</v>
       </c>
       <c r="D10">
@@ -1345,8 +1432,28 @@
       <c r="F10">
         <v>-5</v>
       </c>
-      <c r="G10" t="s">
-        <v>24</v>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11">
+        <v>501</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
